--- a/artfynd/A 44247-2024 artfynd.xlsx
+++ b/artfynd/A 44247-2024 artfynd.xlsx
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122744886</v>
+        <v>122744869</v>
       </c>
       <c r="B10" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,14 +1536,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ögeltjärnen NV, Ång</t>
+          <t>Nybodarna NV, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>664052</v>
+        <v>664133</v>
       </c>
       <c r="R10" t="n">
-        <v>7074174</v>
+        <v>7074239</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,10 +1606,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122744869</v>
+        <v>122744886</v>
       </c>
       <c r="B11" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1642,14 +1642,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Ång</t>
+          <t>Ögeltjärnen NV, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>664133</v>
+        <v>664052</v>
       </c>
       <c r="R11" t="n">
-        <v>7074239</v>
+        <v>7074174</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,7 +1715,7 @@
         <v>122744874</v>
       </c>
       <c r="B12" t="n">
-        <v>90940</v>
+        <v>90944</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>122744877</v>
       </c>
       <c r="B13" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 44247-2024 artfynd.xlsx
+++ b/artfynd/A 44247-2024 artfynd.xlsx
@@ -1606,10 +1606,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122744886</v>
+        <v>122744874</v>
       </c>
       <c r="B11" t="n">
-        <v>90962</v>
+        <v>90944</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1622,34 +1622,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ögeltjärnen NV, Ång</t>
+          <t>Nybodmorarna S, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>664052</v>
+        <v>663851</v>
       </c>
       <c r="R11" t="n">
-        <v>7074174</v>
+        <v>7074229</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,10 +1712,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122744874</v>
+        <v>122744877</v>
       </c>
       <c r="B12" t="n">
-        <v>90944</v>
+        <v>90962</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1728,21 +1728,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>663851</v>
+        <v>663935</v>
       </c>
       <c r="R12" t="n">
-        <v>7074229</v>
+        <v>7074173</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,7 +1818,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122744877</v>
+        <v>122744886</v>
       </c>
       <c r="B13" t="n">
         <v>90962</v>
@@ -1854,14 +1854,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nybodmorarna S, Ång</t>
+          <t>Ögeltjärnen NV, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>663935</v>
+        <v>664052</v>
       </c>
       <c r="R13" t="n">
-        <v>7074173</v>
+        <v>7074174</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 44247-2024 artfynd.xlsx
+++ b/artfynd/A 44247-2024 artfynd.xlsx
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122744869</v>
+        <v>122744874</v>
       </c>
       <c r="B10" t="n">
-        <v>90962</v>
+        <v>90944</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,34 +1516,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Ång</t>
+          <t>Nybodmorarna S, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>664133</v>
+        <v>663851</v>
       </c>
       <c r="R10" t="n">
-        <v>7074239</v>
+        <v>7074229</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,10 +1606,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122744874</v>
+        <v>122744869</v>
       </c>
       <c r="B11" t="n">
-        <v>90944</v>
+        <v>90962</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1622,34 +1622,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nybodmorarna S, Ång</t>
+          <t>Nybodarna NV, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>663851</v>
+        <v>664133</v>
       </c>
       <c r="R11" t="n">
-        <v>7074229</v>
+        <v>7074239</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 44247-2024 artfynd.xlsx
+++ b/artfynd/A 44247-2024 artfynd.xlsx
@@ -1606,7 +1606,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122744869</v>
+        <v>122744877</v>
       </c>
       <c r="B11" t="n">
         <v>90962</v>
@@ -1642,14 +1642,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Ång</t>
+          <t>Nybodmorarna S, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>664133</v>
+        <v>663935</v>
       </c>
       <c r="R11" t="n">
-        <v>7074239</v>
+        <v>7074173</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,7 +1712,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122744877</v>
+        <v>122744869</v>
       </c>
       <c r="B12" t="n">
         <v>90962</v>
@@ -1748,14 +1748,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nybodmorarna S, Ång</t>
+          <t>Nybodarna NV, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>663935</v>
+        <v>664133</v>
       </c>
       <c r="R12" t="n">
-        <v>7074173</v>
+        <v>7074239</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 44247-2024 artfynd.xlsx
+++ b/artfynd/A 44247-2024 artfynd.xlsx
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122744874</v>
+        <v>122744877</v>
       </c>
       <c r="B10" t="n">
-        <v>90944</v>
+        <v>90970</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>663851</v>
+        <v>663935</v>
       </c>
       <c r="R10" t="n">
-        <v>7074229</v>
+        <v>7074173</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,10 +1606,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122744877</v>
+        <v>122744886</v>
       </c>
       <c r="B11" t="n">
-        <v>90962</v>
+        <v>90970</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1642,14 +1642,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nybodmorarna S, Ång</t>
+          <t>Ögeltjärnen NV, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>663935</v>
+        <v>664052</v>
       </c>
       <c r="R11" t="n">
-        <v>7074173</v>
+        <v>7074174</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,10 +1712,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122744869</v>
+        <v>122744874</v>
       </c>
       <c r="B12" t="n">
-        <v>90962</v>
+        <v>90952</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1728,34 +1728,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Ång</t>
+          <t>Nybodmorarna S, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>664133</v>
+        <v>663851</v>
       </c>
       <c r="R12" t="n">
-        <v>7074239</v>
+        <v>7074229</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,10 +1818,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122744886</v>
+        <v>122744869</v>
       </c>
       <c r="B13" t="n">
-        <v>90962</v>
+        <v>90970</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1854,14 +1854,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ögeltjärnen NV, Ång</t>
+          <t>Nybodarna NV, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>664052</v>
+        <v>664133</v>
       </c>
       <c r="R13" t="n">
-        <v>7074174</v>
+        <v>7074239</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 44247-2024 artfynd.xlsx
+++ b/artfynd/A 44247-2024 artfynd.xlsx
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122744877</v>
+        <v>122744874</v>
       </c>
       <c r="B10" t="n">
-        <v>90970</v>
+        <v>90952</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>663935</v>
+        <v>663851</v>
       </c>
       <c r="R10" t="n">
-        <v>7074173</v>
+        <v>7074229</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1712,10 +1712,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122744874</v>
+        <v>122744877</v>
       </c>
       <c r="B12" t="n">
-        <v>90952</v>
+        <v>90970</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1728,21 +1728,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>663851</v>
+        <v>663935</v>
       </c>
       <c r="R12" t="n">
-        <v>7074229</v>
+        <v>7074173</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 44247-2024 artfynd.xlsx
+++ b/artfynd/A 44247-2024 artfynd.xlsx
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122744874</v>
+        <v>122744869</v>
       </c>
       <c r="B10" t="n">
-        <v>90952</v>
+        <v>90970</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,34 +1516,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nybodmorarna S, Ång</t>
+          <t>Nybodarna NV, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>663851</v>
+        <v>664133</v>
       </c>
       <c r="R10" t="n">
-        <v>7074229</v>
+        <v>7074239</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1818,10 +1818,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122744869</v>
+        <v>122744874</v>
       </c>
       <c r="B13" t="n">
-        <v>90970</v>
+        <v>90952</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1834,34 +1834,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Ång</t>
+          <t>Nybodmorarna S, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>664133</v>
+        <v>663851</v>
       </c>
       <c r="R13" t="n">
-        <v>7074239</v>
+        <v>7074229</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 44247-2024 artfynd.xlsx
+++ b/artfynd/A 44247-2024 artfynd.xlsx
@@ -1500,7 +1500,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122744869</v>
+        <v>122744886</v>
       </c>
       <c r="B10" t="n">
         <v>90970</v>
@@ -1536,14 +1536,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Ång</t>
+          <t>Ögeltjärnen NV, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>664133</v>
+        <v>664052</v>
       </c>
       <c r="R10" t="n">
-        <v>7074239</v>
+        <v>7074174</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,10 +1606,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122744886</v>
+        <v>122744874</v>
       </c>
       <c r="B11" t="n">
-        <v>90970</v>
+        <v>90952</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1622,34 +1622,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ögeltjärnen NV, Ång</t>
+          <t>Nybodmorarna S, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>664052</v>
+        <v>663851</v>
       </c>
       <c r="R11" t="n">
-        <v>7074174</v>
+        <v>7074229</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,7 +1712,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122744877</v>
+        <v>122744869</v>
       </c>
       <c r="B12" t="n">
         <v>90970</v>
@@ -1748,14 +1748,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nybodmorarna S, Ång</t>
+          <t>Nybodarna NV, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>663935</v>
+        <v>664133</v>
       </c>
       <c r="R12" t="n">
-        <v>7074173</v>
+        <v>7074239</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,10 +1818,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122744874</v>
+        <v>122744877</v>
       </c>
       <c r="B13" t="n">
-        <v>90952</v>
+        <v>90970</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1834,21 +1834,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1858,10 +1858,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>663851</v>
+        <v>663935</v>
       </c>
       <c r="R13" t="n">
-        <v>7074229</v>
+        <v>7074173</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 44247-2024 artfynd.xlsx
+++ b/artfynd/A 44247-2024 artfynd.xlsx
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122744886</v>
+        <v>122744869</v>
       </c>
       <c r="B10" t="n">
-        <v>90970</v>
+        <v>90973</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,14 +1536,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ögeltjärnen NV, Ång</t>
+          <t>Nybodarna NV, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>664052</v>
+        <v>664133</v>
       </c>
       <c r="R10" t="n">
-        <v>7074174</v>
+        <v>7074239</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,10 +1606,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122744874</v>
+        <v>122744877</v>
       </c>
       <c r="B11" t="n">
-        <v>90952</v>
+        <v>90973</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1622,21 +1622,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>663851</v>
+        <v>663935</v>
       </c>
       <c r="R11" t="n">
-        <v>7074229</v>
+        <v>7074173</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,10 +1712,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122744869</v>
+        <v>122744886</v>
       </c>
       <c r="B12" t="n">
-        <v>90970</v>
+        <v>90973</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1748,14 +1748,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Ång</t>
+          <t>Ögeltjärnen NV, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>664133</v>
+        <v>664052</v>
       </c>
       <c r="R12" t="n">
-        <v>7074239</v>
+        <v>7074174</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,10 +1818,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122744877</v>
+        <v>122744874</v>
       </c>
       <c r="B13" t="n">
-        <v>90970</v>
+        <v>90955</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1834,21 +1834,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1858,10 +1858,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>663935</v>
+        <v>663851</v>
       </c>
       <c r="R13" t="n">
-        <v>7074173</v>
+        <v>7074229</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 44247-2024 artfynd.xlsx
+++ b/artfynd/A 44247-2024 artfynd.xlsx
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122744869</v>
+        <v>122744886</v>
       </c>
       <c r="B10" t="n">
-        <v>90973</v>
+        <v>90975</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,14 +1536,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nybodarna NV, Ång</t>
+          <t>Ögeltjärnen NV, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>664133</v>
+        <v>664052</v>
       </c>
       <c r="R10" t="n">
-        <v>7074239</v>
+        <v>7074174</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,10 +1606,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122744877</v>
+        <v>122744869</v>
       </c>
       <c r="B11" t="n">
-        <v>90973</v>
+        <v>90975</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1642,14 +1642,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nybodmorarna S, Ång</t>
+          <t>Nybodarna NV, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>663935</v>
+        <v>664133</v>
       </c>
       <c r="R11" t="n">
-        <v>7074173</v>
+        <v>7074239</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,10 +1712,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122744886</v>
+        <v>122744874</v>
       </c>
       <c r="B12" t="n">
-        <v>90973</v>
+        <v>90957</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1728,34 +1728,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ögeltjärnen NV, Ång</t>
+          <t>Nybodmorarna S, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>664052</v>
+        <v>663851</v>
       </c>
       <c r="R12" t="n">
-        <v>7074174</v>
+        <v>7074229</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,10 +1818,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122744874</v>
+        <v>122744877</v>
       </c>
       <c r="B13" t="n">
-        <v>90955</v>
+        <v>90975</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1834,21 +1834,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1858,10 +1858,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>663851</v>
+        <v>663935</v>
       </c>
       <c r="R13" t="n">
-        <v>7074229</v>
+        <v>7074173</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
